--- a/out/Attention-S4_repeat_4_000008.xlsx
+++ b/out/Attention-S4_repeat_4_000008.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.7348825055873001</v>
+        <v>1.503542575915647</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.7348825055873001</v>
+        <v>1.503542575915647</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.7348825055873001</v>
+        <v>2.103542575915647</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>4.806964148813837</v>
+        <v>2.103542575915647</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.1348825055873001</v>
+        <v>2.103542575915647</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.1348825055873001</v>
+        <v>2.103542575915647</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.7348825055873001</v>
+        <v>2.103542575915647</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.7348825055873001</v>
+        <v>2.103542575915647</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.7348825055873001</v>
+        <v>2.103542575915647</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.7348825055873001</v>
+        <v>1.503542575915647</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.7348825055873001</v>
+        <v>1.503542575915647</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.7348825055873001</v>
+        <v>1.503542575915647</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.7348825055873001</v>
+        <v>2.103542575915647</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.7867500136927614</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.7348825055873001</v>
+        <v>2.103542575915647</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.7348825055873001</v>
+        <v>2.103542575915647</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.7348825055873001</v>
+        <v>2.103542575915647</v>
       </c>
       <c r="JC45" t="n">
-        <v>-8.323784154909663e-05</v>
+        <v>-0.0001479806622392498</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.09562429263878201</v>
+        <v>-0.1700013586069815</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.7348825055873001</v>
+        <v>2.103542575915647</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.09570753048033116</v>
+        <v>-0.1701493392692208</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.7348825055873001</v>
+        <v>2.103542575915647</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.09570753048033116</v>
+        <v>-0.1701493392692208</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.7348825055873001</v>
+        <v>2.103542575915647</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.09570753048033116</v>
+        <v>-0.1701493392692208</v>
       </c>
     </row>
     <row r="49">
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.7348825055873001</v>
+        <v>2.103542575915647</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.09570753048033116</v>
+        <v>-0.1701493392692208</v>
       </c>
     </row>
     <row r="50">
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.7348825055873001</v>
+        <v>2.103542575915647</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.09570753048033116</v>
+        <v>-0.1701493392692208</v>
       </c>
     </row>
     <row r="51">
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.7348825055873001</v>
+        <v>2.103542575915647</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.09570753048033116</v>
+        <v>-0.1701493392692208</v>
       </c>
     </row>
     <row r="52">
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.7348825055873001</v>
+        <v>1.503542575915647</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.09570753048033116</v>
+        <v>-0.1701493392692208</v>
       </c>
     </row>
     <row r="53">
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.7348825055873001</v>
+        <v>1.503542575915647</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.09570753048033116</v>
+        <v>-0.1701493392692208</v>
       </c>
     </row>
     <row r="54">
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.7348825055873001</v>
+        <v>1.503542575915647</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.09570753048033116</v>
+        <v>-0.1701493392692208</v>
       </c>
     </row>
     <row r="55">
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.7348825055873001</v>
+        <v>1.503542575915647</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.09570753048033116</v>
+        <v>-0.1701493392692208</v>
       </c>
     </row>
     <row r="56">
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.7348825055873001</v>
+        <v>1.503542575915647</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.09570753048033116</v>
+        <v>-0.1701493392692208</v>
       </c>
     </row>
     <row r="57">
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.7348825055873001</v>
+        <v>1.503542575915647</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.09570753048033116</v>
+        <v>-0.1701493392692208</v>
       </c>
     </row>
     <row r="58">
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.7348825055873001</v>
+        <v>1.503542575915647</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.09570753048033116</v>
+        <v>-0.1701493392692208</v>
       </c>
     </row>
     <row r="59">
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.7348825055873001</v>
+        <v>1.503542575915647</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.09578119653908408</v>
+        <v>-0.1702637978301798</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.2648863705228113</v>
+        <v>0.4115666615996745</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.7348825055873001</v>
+        <v>1.503542575915647</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.4345001360377488</v>
+        <v>0.6536602629093812</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.01887309828528821</v>
+        <v>0.02932403822811901</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.7348825055873001</v>
+        <v>1.503542575915647</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.2069350552728742</v>
+        <v>0.300081038684669</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.03309698392933522</v>
+        <v>0.05142437173316745</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.7348825055873001</v>
+        <v>1.503542575915647</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.2542496264551033</v>
+        <v>0.373596141552849</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.04020861496482507</v>
+        <v>0.06247453848569182</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.7348825055873001</v>
+        <v>1.503542575915647</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.3015673474085559</v>
+        <v>0.447116321219736</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01063995219878073</v>
+        <v>0.01653232819520267</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.7348825055873001</v>
+        <v>1.503542575915647</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.2825870964857333</v>
+        <v>0.4176263816925171</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.005908985840662116</v>
+        <v>0.009184057279842683</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>4.806964148813837</v>
+        <v>1.503542575915647</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.2837570335693981</v>
+        <v>0.4194469599233337</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.01241879012609632</v>
+        <v>0.01929832295783005</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>4.806964148813837</v>
+        <v>1.503542575915647</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.3026932422172804</v>
+        <v>0.4488705213361608</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.004875626705987423</v>
+        <v>0.007578743035457382</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.1348825055873001</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.3000156206624682</v>
+        <v>0.4447131925260534</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.003470744297374284</v>
+        <v>0.005395771908227734</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.1348825055873001</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.3020799634292857</v>
+        <v>0.4479228334042251</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.00136375432843636</v>
+        <v>0.002120099726193355</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.301332296411542</v>
+        <v>0.4467644164324326</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.0007718722361727726</v>
+        <v>0.001201926509768414</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.3015114889715938</v>
+        <v>0.4470455727310849</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0002909410461317939</v>
+        <v>0.0004541783691965532</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.3013208777808777</v>
+        <v>0.4467522132796189</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0001337210158704377</v>
+        <v>0.0002107882469095697</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.7348825055873001</v>
+        <v>1.503542575915647</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.3012971682577785</v>
+        <v>0.4467181095770202</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>4.586149354430039e-05</v>
+        <v>7.41178788466895e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.7348825055873001</v>
+        <v>2.103542575915647</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.3012550538618988</v>
+        <v>0.446655376072318</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>9.78655830142907e-06</v>
+        <v>1.837230183129111e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.7867500136927614</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.3012291943831321</v>
+        <v>0.4466179274150703</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>2.631772026544036e-06</v>
+        <v>6.447658039816054e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.7867500136927614</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.3012241824688592</v>
+        <v>0.4466129095436614</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>-8.904788376657899e-07</v>
+        <v>1.164281743501315e-06</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.3012197641348066</v>
+        <v>0.4466088187910742</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-2.211151546177397e-06</v>
+        <v>-8.167273192660964e-07</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.3012162300375547</v>
+        <v>0.4466062013876554</v>
       </c>
     </row>
     <row r="78">
@@ -62943,7 +62943,7 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>-3.752393347619798e-06</v>
+        <v>-3.128590021429696e-06</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.3012109342075505</v>
+        <v>0.4466006841456657</v>
       </c>
     </row>
     <row r="79">
@@ -63738,7 +63738,7 @@
         <v>0</v>
       </c>
       <c r="IY79" t="n">
-        <v>-4.70653621650487e-06</v>
+        <v>-4.413072433009741e-06</v>
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.3012052722105468</v>
+        <v>0.4465943601516578</v>
       </c>
     </row>
     <row r="80">
@@ -64533,7 +64533,7 @@
         <v>0</v>
       </c>
       <c r="IY80" t="n">
-        <v>0</v>
+        <v>-4.890058184668745e-06</v>
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.3012050884680876</v>
+        <v>0.4465889923630795</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.7348825055873001</v>
+        <v>2.103542575915647</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.3012051252165793</v>
+        <v>0.4465890291115712</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.7348825055873001</v>
+        <v>2.103542575915647</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.3012052354620549</v>
+        <v>0.4465891393570467</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.7348825055873001</v>
+        <v>2.103542575915647</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.3012053089590385</v>
+        <v>0.4465892128540303</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.7348825055873001</v>
+        <v>2.103542575915647</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.3012054927014976</v>
+        <v>0.4465893965964895</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>4.806964148813837</v>
+        <v>-0.7867500136927614</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.3012070361381541</v>
+        <v>0.4465909400331459</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.1348825055873001</v>
+        <v>2.103542575915647</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.3012085060778272</v>
+        <v>0.446592409972819</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>4.806964148813837</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.3012097555265492</v>
+        <v>0.4465936594215411</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>4.806964148813837</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.3012111152207465</v>
+        <v>0.4465950191157383</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>4.806964148813837</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.3012089103112372</v>
+        <v>0.446592814206229</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>4.806964148813837</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.3012085060778272</v>
+        <v>0.446592409972819</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>4.806964148813837</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.3012076608625152</v>
+        <v>0.4465915647575071</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.1348825055873001</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.3012082120898925</v>
+        <v>0.4465921159848843</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.3012078813534661</v>
+        <v>0.4465917852484579</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.3012075873655316</v>
+        <v>0.4465914912605234</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.3012076608625152</v>
+        <v>0.4465915647575071</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.3012072198806133</v>
+        <v>0.4465911237756051</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.3012071096351377</v>
+        <v>0.4465910135301296</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.3012070728866461</v>
+        <v>0.4465909767816379</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.3012072198806133</v>
+        <v>0.4465911237756051</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>4.806964148813837</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.3012067421502196</v>
+        <v>0.4465906460452115</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>4.806964148813837</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.3012076976110069</v>
+        <v>0.4465916015059987</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.1348825055873001</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.3012076608625152</v>
+        <v>0.4465915647575071</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.1348825055873001</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.3012073301260888</v>
+        <v>0.4465912340210806</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.3012077711079907</v>
+        <v>0.4465916750029826</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.3012071463836297</v>
+        <v>0.4465910502786215</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.3012069626411705</v>
+        <v>0.4465908665361623</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.3012065584077604</v>
+        <v>0.4465904623027523</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.3012057131924485</v>
+        <v>0.4465896170874403</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.3012056764439568</v>
+        <v>0.4465895803389486</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.301205823437924</v>
+        <v>0.4465897273329159</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.3012057499409404</v>
+        <v>0.4465896538359322</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.301205823437924</v>
+        <v>0.4465897273329159</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.3012058601864159</v>
+        <v>0.4465897640814078</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.3012057499409404</v>
+        <v>0.4465896538359322</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.3012061909228423</v>
+        <v>0.4465900948178342</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.3012060806773668</v>
+        <v>0.4465899845723587</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.3012060439288749</v>
+        <v>0.4465899478238667</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.3012059704318913</v>
+        <v>0.4465898743268831</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.3012059336833996</v>
+        <v>0.4465898375783914</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.3012057131924485</v>
+        <v>0.4465896170874403</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.3012056396954649</v>
+        <v>0.4465895435904567</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.3012055661984813</v>
+        <v>0.4465894700934731</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-1.386750013692762</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.3012056029469732</v>
+        <v>0.446589506841965</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.7348825055873001</v>
+        <v>2.103542575915647</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.3012054927014976</v>
+        <v>0.4465893965964895</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.7348825055873001</v>
+        <v>2.103542575915647</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.3012056029469732</v>
+        <v>0.446589506841965</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.7348825055873001</v>
+        <v>2.103542575915647</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.3012058969349076</v>
+        <v>0.4465898008298995</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-S4_repeat_4_000008.xlsx
+++ b/out/Attention-S4_repeat_4_000008.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.7348825055873001</v>
+        <v>0.9211965688743772</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>4.806964148813837</v>
+        <v>0.9211965688743772</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.1348825055873001</v>
+        <v>0.9211965688743772</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.1348825055873001</v>
+        <v>-0.1382051466884344</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.1382051466884344</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,10 +36719,10 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC45" t="n">
-        <v>-8.323784154909663e-05</v>
+        <v>-9.228552213218063e-05</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.09562429263878201</v>
+        <v>-0.1060183398614423</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.09570753048033116</v>
+        <v>-0.1061106253835745</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.09570753048033116</v>
+        <v>-0.1061106253835745</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.09570753048033116</v>
+        <v>-0.1061106253835745</v>
       </c>
     </row>
     <row r="49">
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.09570753048033116</v>
+        <v>-0.1061106253835745</v>
       </c>
     </row>
     <row r="50">
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.09570753048033116</v>
+        <v>-0.1061106253835745</v>
       </c>
     </row>
     <row r="51">
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.09570753048033116</v>
+        <v>-0.1061106253835745</v>
       </c>
     </row>
     <row r="52">
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.09570753048033116</v>
+        <v>-0.1061106253835745</v>
       </c>
     </row>
     <row r="53">
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.09570753048033116</v>
+        <v>-0.1061106253835745</v>
       </c>
     </row>
     <row r="54">
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.09570753048033116</v>
+        <v>-0.1061106253835745</v>
       </c>
     </row>
     <row r="55">
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.09570753048033116</v>
+        <v>-0.1061106253835745</v>
       </c>
     </row>
     <row r="56">
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.09570753048033116</v>
+        <v>-0.1061106253835745</v>
       </c>
     </row>
     <row r="57">
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.09570753048033116</v>
+        <v>-0.1061106253835745</v>
       </c>
     </row>
     <row r="58">
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.09570753048033116</v>
+        <v>-0.1061106253835745</v>
       </c>
     </row>
     <row r="59">
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.09578119653908408</v>
+        <v>-0.1061923883939693</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.2648863705228113</v>
+        <v>0.2940009078751388</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.4345001360377488</v>
+        <v>0.4823744343442586</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.01887309828528821</v>
+        <v>0.02094753954513763</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.2069350552728742</v>
+        <v>0.2297964815165277</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.03309698392933522</v>
+        <v>0.03673484709317544</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.2542496264551033</v>
+        <v>0.2823116454773688</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.04020861496482507</v>
+        <v>0.04462850086719445</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.3015673474085559</v>
+        <v>0.3348303047783959</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01063995219878073</v>
+        <v>0.01180965449229713</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.7348825055873001</v>
+        <v>0.9211965688743772</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.2825870964857333</v>
+        <v>0.3137644644979364</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.005908985840662116</v>
+        <v>0.006559084036050035</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>4.806964148813837</v>
+        <v>1.980598284437189</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.2837570335693981</v>
+        <v>0.3150635531569068</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.01241879012609632</v>
+        <v>0.01378448219206671</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>4.806964148813837</v>
+        <v>1.980598284437189</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.3026932422172804</v>
+        <v>0.3360817554733728</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.004875626705987423</v>
+        <v>0.005412132321558745</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.1348825055873001</v>
+        <v>0.9211965688743772</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.3000156206624682</v>
+        <v>0.3331103808583755</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.003470744297374284</v>
+        <v>0.003853679897382767</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.1348825055873001</v>
+        <v>-0.1382051466884344</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.3020799634292857</v>
+        <v>0.3354021396078069</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.00136375432843636</v>
+        <v>0.001513122360309375</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.301332296411542</v>
+        <v>0.3345730600932879</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.0007718722361727726</v>
+        <v>0.0008566499603582932</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.3015114889715938</v>
+        <v>0.3347725367743764</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0002909410461317939</v>
+        <v>0.0003238233845908821</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.3013208777808777</v>
+        <v>0.3345613021180248</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0001337210158704377</v>
+        <v>0.0001491344620782641</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.3012971682577785</v>
+        <v>0.3345355137590256</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>4.586149354430039e-05</v>
+        <v>5.151277060477821e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.3012550538618988</v>
+        <v>0.3344892755413815</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>9.78655830142907e-06</v>
+        <v>1.169450130806508e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.3012291943831321</v>
+        <v>0.3344610979290616</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>2.631772026544036e-06</v>
+        <v>3.108757778203038e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.3012241824688592</v>
+        <v>0.3344560852701471</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>-8.904788376657899e-07</v>
+        <v>-3.767886923740136e-07</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.3012197641348066</v>
+        <v>0.3344517396443377</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.3012162300375547</v>
+        <v>0.3344483892895449</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.3012109342075505</v>
+        <v>0.3344430199625572</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.3012052722105468</v>
+        <v>0.3344370272291268</v>
       </c>
     </row>
     <row r="80">
@@ -64533,7 +64533,7 @@
         <v>0</v>
       </c>
       <c r="IY80" t="n">
-        <v>0</v>
+        <v>-4.890058184668745e-06</v>
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.3012050884680876</v>
+        <v>0.3344316594405484</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.3012051252165793</v>
+        <v>0.3344316961890401</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.3012052354620549</v>
+        <v>0.3344318064345156</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.3012053089590385</v>
+        <v>0.3344318799314993</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.7348825055873001</v>
+        <v>0.9211965688743772</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.3012054927014976</v>
+        <v>0.3344320636739584</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>4.806964148813837</v>
+        <v>0.9211965688743772</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.3012070361381541</v>
+        <v>0.3344336071106149</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.1348825055873001</v>
+        <v>1.980598284437189</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.3012085060778272</v>
+        <v>0.334435077050288</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>4.806964148813837</v>
+        <v>1.980598284437189</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.3012097555265492</v>
+        <v>0.33443632649901</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>4.806964148813837</v>
+        <v>3.04</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.3012111152207465</v>
+        <v>0.3344376861932073</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>4.806964148813837</v>
+        <v>3.04</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.3012089103112372</v>
+        <v>0.334435481283698</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>4.806964148813837</v>
+        <v>3.04</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.3012085060778272</v>
+        <v>0.334435077050288</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>4.806964148813837</v>
+        <v>1.980598284437189</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.3012076608625152</v>
+        <v>0.334434231834976</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.1348825055873001</v>
+        <v>0.9211965688743772</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.3012082120898925</v>
+        <v>0.3344347830623532</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.3012078813534661</v>
+        <v>0.3344344523259268</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.3012075873655316</v>
+        <v>0.3344341583379924</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.3012076608625152</v>
+        <v>0.334434231834976</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.3012072198806133</v>
+        <v>0.3344337908530741</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.3012071096351377</v>
+        <v>0.3344336806075985</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.3012070728866461</v>
+        <v>0.3344336438591068</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.7348825055873001</v>
+        <v>0.7211965688743771</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.3012072198806133</v>
+        <v>0.3344337908530741</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>4.806964148813837</v>
+        <v>1.980598284437189</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.3012067421502196</v>
+        <v>0.3344333131226804</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>4.806964148813837</v>
+        <v>1.980598284437189</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.3012076976110069</v>
+        <v>0.3344342685834677</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.1348825055873001</v>
+        <v>0.9211965688743772</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.3012076608625152</v>
+        <v>0.334434231834976</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.1348825055873001</v>
+        <v>-0.1382051466884344</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.3012073301260888</v>
+        <v>0.3344339010985496</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.3012077711079907</v>
+        <v>0.3344343420804515</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.3012071463836297</v>
+        <v>0.3344337173560905</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.3012069626411705</v>
+        <v>0.3344335336136313</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.3012065584077604</v>
+        <v>0.3344331293802212</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.3012057131924485</v>
+        <v>0.3344322841649093</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.3012056764439568</v>
+        <v>0.3344322474164176</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.301205823437924</v>
+        <v>0.3344323944103848</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.3012057499409404</v>
+        <v>0.3344323209134012</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.301205823437924</v>
+        <v>0.3344323944103848</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.3012058601864159</v>
+        <v>0.3344324311588767</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.3012057499409404</v>
+        <v>0.3344323209134012</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.3012061909228423</v>
+        <v>0.3344327618953031</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.3012060806773668</v>
+        <v>0.3344326516498276</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.3012060439288749</v>
+        <v>0.3344326149013357</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.3012059704318913</v>
+        <v>0.3344325414043521</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.3012059336833996</v>
+        <v>0.3344325046558604</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.3012057131924485</v>
+        <v>0.3344322841649093</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.3012056396954649</v>
+        <v>0.3344322106679257</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.3012055661984813</v>
+        <v>0.3344321371709421</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.3012056029469732</v>
+        <v>0.334432173919434</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.3012054927014976</v>
+        <v>0.3344320636739584</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.3012056029469732</v>
+        <v>0.334432173919434</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.7348825055873001</v>
+        <v>-0.3382051466884344</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.3012058969349076</v>
+        <v>0.3344324679073684</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-S4_repeat_4_000008.xlsx
+++ b/out/Attention-S4_repeat_4_000008.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.004105569794774055</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.5799999999999997</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.004199685528874397</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.2999999999999997</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>-0.001076998189091682</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.9211965688743772</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.001579036936163902</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.9211965688743772</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.001621142029762268</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.9211965688743772</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.004720171913504601</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.1382051466884344</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.00409243255853653</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.1382051466884344</v>
+        <v>0.3</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.003756960853934288</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.002779493108391762</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.004044504836201668</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.004785140976309776</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-0.005172261968255043</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>-0.004879724234342575</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>-0.005398686975240707</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>-0.003740677610039711</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>-0.003687802702188492</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>-0.004451440647244453</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>-0.004574047401547432</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>-0.004240764304995537</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>-0.003628205507993698</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>-0.004320899024605751</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>-0.004484027624130249</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>-0.004538767039775848</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>-0.004077451303601265</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.3382051466884344</v>
+        <v>0.16</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>-0.004067542031407356</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.3382051466884344</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>-0.003363519906997681</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.3382051466884344</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>-0.003143677487969398</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.3382051466884344</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>-0.003746559843420982</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.3382051466884344</v>
+        <v>0.3</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>-0.004884639754891396</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.3382051466884344</v>
+        <v>0.3</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>-0.005529161542654037</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.3382051466884344</v>
+        <v>0.16</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>-0.0009116083383560181</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>-0.003517614677548409</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>-0.005515797063708305</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>-0.006349947303533554</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>-0.006662052124738693</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>-0.005180539563298225</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>-0.006106594577431679</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>-0.007302790880203247</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>-0.006528204306960106</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>-0.008216904476284981</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>-0.009229995310306549</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0</v>
+        <v>-0.009110245853662491</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0</v>
+        <v>-0.006795920431613922</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>-0.005018945783376694</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC45" t="n">
-        <v>-9.228552213218063e-05</v>
+        <v>-9.726282245968469e-05</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1060183398614423</v>
+        <v>-0.1117363019591274</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>-0.008859200403094292</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1061106253835745</v>
+        <v>-0.1118335647815871</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.005307916551828384</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1061106253835745</v>
+        <v>-0.1118335647815871</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.01057109609246254</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1061106253835745</v>
+        <v>-0.1118335647815871</v>
       </c>
     </row>
     <row r="49">
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.00807705894112587</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1061106253835745</v>
+        <v>-0.1118335647815871</v>
       </c>
     </row>
     <row r="50">
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.01036790199577808</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1061106253835745</v>
+        <v>-0.1118335647815871</v>
       </c>
     </row>
     <row r="51">
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.009826954454183578</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1061106253835745</v>
+        <v>-0.1118335647815871</v>
       </c>
     </row>
     <row r="52">
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.01114511396735907</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1061106253835745</v>
+        <v>-0.1118335647815871</v>
       </c>
     </row>
     <row r="53">
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.01051313616335392</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1061106253835745</v>
+        <v>-0.1118335647815871</v>
       </c>
     </row>
     <row r="54">
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.01101155951619148</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1061106253835745</v>
+        <v>-0.1118335647815871</v>
       </c>
     </row>
     <row r="55">
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.009344510734081268</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1061106253835745</v>
+        <v>-0.1118335647815871</v>
       </c>
     </row>
     <row r="56">
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>-0.009883230552077293</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1061106253835745</v>
+        <v>-0.1118335647815871</v>
       </c>
     </row>
     <row r="57">
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.009758871048688889</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1061106253835745</v>
+        <v>-0.1118335647815871</v>
       </c>
     </row>
     <row r="58">
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>-0.008941499516367912</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.3382051466884344</v>
+        <v>0.16</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1061106253835745</v>
+        <v>-0.1118335647815871</v>
       </c>
     </row>
     <row r="59">
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>-0.00504004955291748</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.3382051466884344</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1061923883939693</v>
+        <v>-0.1119322391457725</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.2940009078751388</v>
+        <v>0.3548102847049715</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.007029589265584946</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.3382051466884344</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.4823744343442586</v>
+        <v>0.5983700934823972</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.02094753954513763</v>
+        <v>0.02528015829070885</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.006790531799197197</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.3382051466884344</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.2297964815165277</v>
+        <v>0.293550529735771</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.03673484709317544</v>
+        <v>0.04433291247791291</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.003962175920605659</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.3382051466884344</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.2823116454773688</v>
+        <v>0.3569276866280812</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.04462850086719445</v>
+        <v>0.05385925298524948</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.006097197532653809</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.3382051466884344</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.3348303047783959</v>
+        <v>0.4203090618205294</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01180965449229713</v>
+        <v>0.01425250779410753</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.005791019648313522</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.9211965688743772</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.3137644644979364</v>
+        <v>0.3948860604179755</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.006559084036050035</v>
+        <v>0.007916879420435301</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.0003343969583511353</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.980598284437189</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.3150635531569068</v>
+        <v>0.3964548583669453</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.01378448219206671</v>
+        <v>0.01663563515272543</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.00143338181078434</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.980598284437189</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.3360817554733728</v>
+        <v>0.4218198772612645</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.005412132321558745</v>
+        <v>0.006532375424049656</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>-0.00203632190823555</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.9211965688743772</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.3331103808583755</v>
+        <v>0.4182351356470096</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.003853679897382767</v>
+        <v>0.004650599929832851</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.003505147993564606</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.1382051466884344</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.3354021396078069</v>
+        <v>0.4210017506465547</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.001513122360309375</v>
+        <v>0.001828153118441553</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.002537503838539124</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.3382051466884344</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.3345730600932879</v>
+        <v>0.4200021073192193</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.0008566499603582932</v>
+        <v>0.001035453887731392</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.004402708262205124</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.3347725367743764</v>
+        <v>0.4202437937835748</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0003238233845908821</v>
+        <v>0.0003907624307397402</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.005234973505139351</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.16</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.3345613021180248</v>
+        <v>0.4199902081586907</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0001491344620782641</v>
+        <v>0.0001810623149373331</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.005644770339131355</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.3</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.3345355137590256</v>
+        <v>0.4199601136396134</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>5.151277060477821e-05</v>
+        <v>6.281532472573384e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.004821334034204483</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.3</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.3344892755413815</v>
+        <v>0.4199053337905055</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>1.169450130806508e-05</v>
+        <v>1.503340156967809e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.005257934331893921</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.3</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.3344610979290616</v>
+        <v>0.4198721899192953</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>3.108757778203038e-06</v>
+        <v>5.016700784839047e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.005390523001551628</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.16</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.3344560852701471</v>
+        <v>0.4198671742818125</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>-3.767886923740136e-07</v>
+        <v>6.505915982095382e-07</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.006039014086127281</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.3344517396443377</v>
+        <v>0.4198629740724901</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-2.211151546177397e-06</v>
+        <v>-1.513939432721747e-06</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.003841942176222801</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.3382051466884344</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.3344483892895449</v>
+        <v>0.4198599901933845</v>
       </c>
     </row>
     <row r="78">
@@ -62943,7 +62943,7 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>-3.752393347619798e-06</v>
+        <v>-3.128590021429696e-06</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.003702661022543907</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.3382051466884344</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.3344430199625572</v>
+        <v>0.4198545464483781</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.003586774691939354</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.3382051466884344</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.3344370272291268</v>
+        <v>0.4198485537149478</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.003710998222231865</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.3382051466884344</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.3344316594405484</v>
+        <v>0.4198431859263694</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.004140488803386688</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.3382051466884344</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.3344316961890401</v>
+        <v>0.4198432226748611</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.003966702148318291</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.3382051466884344</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.3344318064345156</v>
+        <v>0.4198433329203367</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.002582358196377754</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.3382051466884344</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.3344318799314993</v>
+        <v>0.4198434064173203</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.003689371049404144</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.9211965688743772</v>
+        <v>-0.16</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.3344320636739584</v>
+        <v>0.4198435901597794</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.0003882013261318207</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.9211965688743772</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.3344336071106149</v>
+        <v>0.4198451335964359</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.006339980289340019</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.980598284437189</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.334435077050288</v>
+        <v>0.419846603536109</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.005652716383337975</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.980598284437189</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.33443632649901</v>
+        <v>0.419847852984831</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.05976185947656631</v>
       </c>
       <c r="JB88" t="n">
-        <v>3.04</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.3344376861932073</v>
+        <v>0.4198492126790283</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.003237888216972351</v>
       </c>
       <c r="JB89" t="n">
-        <v>3.04</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.334435481283698</v>
+        <v>0.419847007769519</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.01083877496421337</v>
       </c>
       <c r="JB90" t="n">
-        <v>3.04</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.334435077050288</v>
+        <v>0.419846603536109</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0.002693260088562965</v>
       </c>
       <c r="JB91" t="n">
-        <v>1.980598284437189</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.334434231834976</v>
+        <v>0.419845758320797</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.0001458078622817993</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.9211965688743772</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.3344347830623532</v>
+        <v>0.4198463095481743</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.0009783226996660233</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.3</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.3344344523259268</v>
+        <v>0.4198459788117478</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.001420676708221436</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.3344341583379924</v>
+        <v>0.4198456848238134</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.002163557335734367</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.334434231834976</v>
+        <v>0.419845758320797</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.004232967272400856</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.3344337908530741</v>
+        <v>0.4198453173388951</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.003160117194056511</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.3344336806075985</v>
+        <v>0.4198452070934195</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.002832928672432899</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.3344336438591068</v>
+        <v>0.4198451703449278</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.002167070284485817</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.7211965688743771</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.3344337908530741</v>
+        <v>0.4198453173388951</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.004029830917716026</v>
       </c>
       <c r="JB100" t="n">
-        <v>1.980598284437189</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.3344333131226804</v>
+        <v>0.4198448396085014</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.01007555238902569</v>
       </c>
       <c r="JB101" t="n">
-        <v>1.980598284437189</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.3344342685834677</v>
+        <v>0.4198457950692887</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.00199468620121479</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.9211965688743772</v>
+        <v>0.16</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.334434231834976</v>
+        <v>0.419845758320797</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.002634992823004723</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.1382051466884344</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.3344339010985496</v>
+        <v>0.4198454275843706</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.003281893208622932</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.3344343420804515</v>
+        <v>0.4198458685662725</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.004114734008908272</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.3344337173560905</v>
+        <v>0.4198452438419114</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.00523664616048336</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.3344335336136313</v>
+        <v>0.4198450600994523</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.005342314019799232</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.3344331293802212</v>
+        <v>0.4198446558660422</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.006966009736061096</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.3344322841649093</v>
+        <v>0.4198438106507303</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.007673727348446846</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.3344322474164176</v>
+        <v>0.4198437739022386</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.006034348160028458</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.3344323944103848</v>
+        <v>0.4198439208962058</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.006065120920538902</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.3344323209134012</v>
+        <v>0.4198438473992222</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.00213765911757946</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.3344323944103848</v>
+        <v>0.4198439208962058</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.005784882232546806</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.3344324311588767</v>
+        <v>0.4198439576446977</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.004620019346475601</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.3344323209134012</v>
+        <v>0.4198438473992222</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.004877703264355659</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.3344327618953031</v>
+        <v>0.4198442883811241</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.005756128579378128</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.3344326516498276</v>
+        <v>0.4198441781356486</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.006123313680291176</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.3344326149013357</v>
+        <v>0.4198441413871567</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.006761843338608742</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.3344325414043521</v>
+        <v>0.419844067890173</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.008412795141339302</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.3344325046558604</v>
+        <v>0.4198440311416813</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.005559289827942848</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.3344322841649093</v>
+        <v>0.4198438106507303</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.005189951509237289</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.3382051466884344</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.3344322106679257</v>
+        <v>0.4198437371537467</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.004353756085038185</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.3382051466884344</v>
+        <v>0.16</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.3344321371709421</v>
+        <v>0.419843663656763</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.003113849088549614</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.3382051466884344</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.334432173919434</v>
+        <v>0.419843700405255</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.002545749768614769</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.3382051466884344</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.3344320636739584</v>
+        <v>0.4198435901597794</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.00201515294611454</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.3382051466884344</v>
+        <v>1</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.334432173919434</v>
+        <v>0.419843700405255</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.002892835065722466</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.3382051466884344</v>
+        <v>1.28</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.3344324679073684</v>
+        <v>0.4198439943931894</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-S4_repeat_4_000008.xlsx
+++ b/out/Attention-S4_repeat_4_000008.xlsx
@@ -73289,7 +73289,7 @@
         <v>0.002693260088562965</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.7199999999999999</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC91" t="n">
         <v>0.419845758320797</v>
@@ -74084,7 +74084,7 @@
         <v>-0.0001458078622817993</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.5799999999999998</v>
+        <v>-0.3</v>
       </c>
       <c r="JC92" t="n">
         <v>0.4198463095481743</v>
@@ -74879,7 +74879,7 @@
         <v>-0.0009783226996660233</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.3</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC93" t="n">
         <v>0.4198459788117478</v>
@@ -75674,7 +75674,7 @@
         <v>-0.001420676708221436</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.5799999999999998</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC94" t="n">
         <v>0.4198456848238134</v>
@@ -76469,7 +76469,7 @@
         <v>-0.002163557335734367</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.7199999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC95" t="n">
         <v>0.419845758320797</v>
@@ -77264,7 +77264,7 @@
         <v>-0.004232967272400856</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.8599999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC96" t="n">
         <v>0.4198453173388951</v>
@@ -80444,7 +80444,7 @@
         <v>0.004029830917716026</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.4399999999999999</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC100" t="n">
         <v>0.4198448396085014</v>
